--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/KENTUCKY_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/KENTUCKY_2020.xlsx
@@ -1237,7 +1237,7 @@
         <v>23</v>
       </c>
       <c r="D49">
-        <v>0.009019607843137255</v>
+        <v>0.009019607843137257</v>
       </c>
     </row>
     <row r="50">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C120">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C161">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C165">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C170">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C278">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C394">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C449">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C496">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C540">
@@ -13027,7 +13027,7 @@
         <v>23</v>
       </c>
       <c r="D704">
-        <v>0.009019607843137255</v>
+        <v>0.009019607843137257</v>
       </c>
     </row>
     <row r="705">
@@ -13243,7 +13243,7 @@
         <v>23</v>
       </c>
       <c r="D716">
-        <v>0.009019607843137255</v>
+        <v>0.009019607843137257</v>
       </c>
     </row>
     <row r="717">
